--- a/week-02/Ex2A_events_normalized.xlsx
+++ b/week-02/Ex2A_events_normalized.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luise\Documents\DataAnalytics\week-02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DECD202-A531-4288-A703-CCCC703D9E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4591703B-AA1A-4420-891C-F1726A233242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{5091876E-AF08-41C4-B976-D2AB9D8B455C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="134">
   <si>
     <t>Event ID</t>
   </si>
@@ -420,6 +420,22 @@
   </si>
   <si>
     <t>Location</t>
+  </si>
+  <si>
+    <t>Location ID</t>
+  </si>
+  <si>
+    <t>Managers</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>5th table</t>
+  </si>
+  <si>
+    <t>AI was able to spot major oversights that occurred on my end and I was able to better normalize the data and eliminate
+a lot of repeating information</t>
   </si>
 </sst>
 </file>
@@ -562,7 +578,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -751,6 +767,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -924,13 +958,20 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1306,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA38BEC-78EC-44DC-83F3-AA711D021920}">
-  <dimension ref="A1:Q67"/>
+  <dimension ref="A1:Q95"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" customWidth="1"/>
@@ -1974,316 +2015,280 @@
         <v>126</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B17" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E17" t="s">
         <v>1</v>
       </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="F17" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>2</v>
       </c>
-      <c r="G17" t="s">
-        <v>105</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="H17" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="I17" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>102</v>
       </c>
       <c r="C18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
         <v>3</v>
       </c>
-      <c r="D18" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18">
+      <c r="F18">
         <v>7</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
         <v>46095</v>
-      </c>
-      <c r="G18" t="s">
-        <v>6</v>
       </c>
       <c r="H18" t="s">
         <v>108</v>
       </c>
-      <c r="I18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>103</v>
       </c>
       <c r="C19" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19" t="s">
         <v>7</v>
       </c>
-      <c r="D19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19">
+      <c r="F19">
         <v>7</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>46194</v>
-      </c>
-      <c r="G19" t="s">
-        <v>9</v>
       </c>
       <c r="H19" t="s">
         <v>109</v>
       </c>
-      <c r="I19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>104</v>
       </c>
       <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" t="s">
         <v>10</v>
       </c>
-      <c r="D20" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20">
+      <c r="F20">
         <v>2</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
         <v>46115</v>
-      </c>
-      <c r="G20" t="s">
-        <v>13</v>
       </c>
       <c r="H20" t="s">
         <v>110</v>
       </c>
-      <c r="I20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>105</v>
       </c>
       <c r="C21" t="s">
+        <v>118</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
         <v>14</v>
       </c>
-      <c r="D21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21">
+      <c r="F21">
         <v>3</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>46157</v>
-      </c>
-      <c r="G21" t="s">
-        <v>9</v>
       </c>
       <c r="H21" t="s">
         <v>109</v>
       </c>
-      <c r="I21" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B22">
         <v>106</v>
       </c>
       <c r="C22" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
         <v>17</v>
       </c>
-      <c r="D22" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22">
+      <c r="F22">
         <v>6</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
         <v>46109</v>
-      </c>
-      <c r="G22" t="s">
-        <v>20</v>
       </c>
       <c r="H22" t="s">
         <v>125</v>
       </c>
-      <c r="I22" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>107</v>
       </c>
       <c r="C23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
         <v>21</v>
       </c>
-      <c r="D23" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23">
+      <c r="F23">
         <v>4</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>46130</v>
-      </c>
-      <c r="G23" t="s">
-        <v>23</v>
       </c>
       <c r="H23" t="s">
         <v>111</v>
       </c>
-      <c r="I23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>108</v>
       </c>
       <c r="C24" t="s">
+        <v>120</v>
+      </c>
+      <c r="D24">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
         <v>24</v>
       </c>
-      <c r="D24" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24">
+      <c r="F24">
         <v>5</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
         <v>46144</v>
-      </c>
-      <c r="G24" t="s">
-        <v>13</v>
       </c>
       <c r="H24" t="s">
         <v>110</v>
       </c>
-      <c r="I24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>109</v>
       </c>
       <c r="C25" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
         <v>27</v>
       </c>
-      <c r="D25" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25">
+      <c r="F25">
         <v>3</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
         <v>46181</v>
-      </c>
-      <c r="G25" t="s">
-        <v>29</v>
       </c>
       <c r="H25" t="s">
         <v>112</v>
       </c>
-      <c r="I25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B26">
         <v>110</v>
       </c>
       <c r="C26" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
         <v>30</v>
       </c>
-      <c r="D26" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26">
+      <c r="F26">
         <v>7</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
         <v>46215</v>
-      </c>
-      <c r="G26" t="s">
-        <v>9</v>
       </c>
       <c r="H26" t="s">
         <v>109</v>
       </c>
-      <c r="I26" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>111</v>
       </c>
       <c r="C27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27" t="s">
         <v>31</v>
       </c>
-      <c r="D27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27">
+      <c r="F27">
         <v>2</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G27" s="1">
         <v>46102</v>
-      </c>
-      <c r="G27" t="s">
-        <v>13</v>
       </c>
       <c r="H27" t="s">
         <v>110</v>
       </c>
-      <c r="I27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B28">
         <v>112</v>
       </c>
       <c r="C28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
         <v>33</v>
       </c>
-      <c r="D28" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28">
+      <c r="F28">
         <v>1</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
         <v>46137</v>
-      </c>
-      <c r="G28" t="s">
-        <v>20</v>
       </c>
       <c r="H28" t="s">
         <v>125</v>
-      </c>
-      <c r="I28" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -2395,292 +2400,416 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="D40" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="F40" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="H40" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D41" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F41" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="F42" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="F43" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="H43" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B44" t="s">
-        <v>122</v>
-      </c>
-      <c r="C44" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" t="s">
-        <v>97</v>
-      </c>
-      <c r="F44" t="s">
-        <v>82</v>
-      </c>
       <c r="H44" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B45" t="s">
-        <v>123</v>
-      </c>
-      <c r="C45" t="s">
-        <v>34</v>
-      </c>
-      <c r="D45" t="s">
-        <v>87</v>
-      </c>
-      <c r="F45" t="s">
-        <v>88</v>
-      </c>
-      <c r="H45" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="H46" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B49" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" t="s">
+        <v>91</v>
+      </c>
+      <c r="E49" t="s">
+        <v>92</v>
+      </c>
+      <c r="F49" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B51" s="5" t="s">
-        <v>90</v>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" t="s">
+        <v>43</v>
+      </c>
+      <c r="E50" t="s">
+        <v>44</v>
+      </c>
+      <c r="F50">
+        <v>90026</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B51">
+        <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>91</v>
+        <v>47</v>
       </c>
       <c r="D51" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="E51" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B52" t="s">
-        <v>42</v>
+        <v>49</v>
+      </c>
+      <c r="F51">
+        <v>78741</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B52">
+        <v>3</v>
       </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="D52" t="s">
+        <v>54</v>
+      </c>
+      <c r="E52" t="s">
         <v>44</v>
       </c>
-      <c r="E52">
-        <v>90026</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B53" t="s">
-        <v>47</v>
+      <c r="F52">
+        <v>90046</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B53">
+        <v>4</v>
       </c>
       <c r="C53" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D53" t="s">
-        <v>49</v>
-      </c>
-      <c r="E53">
-        <v>78741</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B54" t="s">
-        <v>53</v>
+        <v>58</v>
+      </c>
+      <c r="E53" t="s">
+        <v>59</v>
+      </c>
+      <c r="F53">
+        <v>60616</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B54">
+        <v>5</v>
       </c>
       <c r="C54" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="D54" t="s">
-        <v>44</v>
-      </c>
-      <c r="E54">
-        <v>90046</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B55" t="s">
-        <v>57</v>
+        <v>64</v>
+      </c>
+      <c r="E54" t="s">
+        <v>65</v>
+      </c>
+      <c r="F54">
+        <v>10011</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B55">
+        <v>7</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D55" t="s">
-        <v>59</v>
-      </c>
-      <c r="E55">
-        <v>60616</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B56" t="s">
-        <v>63</v>
+        <v>70</v>
+      </c>
+      <c r="E55" t="s">
+        <v>71</v>
+      </c>
+      <c r="F55">
+        <v>97214</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B56">
+        <v>8</v>
       </c>
       <c r="C56" t="s">
+        <v>75</v>
+      </c>
+      <c r="D56" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" t="s">
+        <v>77</v>
+      </c>
+      <c r="F56">
+        <v>48226</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B57">
+        <v>10</v>
+      </c>
+      <c r="C57" t="s">
+        <v>81</v>
+      </c>
+      <c r="D57" t="s">
         <v>64</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E57" t="s">
         <v>65</v>
       </c>
-      <c r="E56">
-        <v>10011</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B57" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" t="s">
-        <v>58</v>
-      </c>
-      <c r="D57" t="s">
-        <v>59</v>
-      </c>
-      <c r="E57">
-        <v>60616</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B58" t="s">
-        <v>69</v>
+      <c r="F57">
+        <v>10012</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B58">
+        <v>11</v>
       </c>
       <c r="C58" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="D58" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58">
-        <v>97214</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C59" t="s">
-        <v>76</v>
-      </c>
-      <c r="D59" t="s">
-        <v>77</v>
-      </c>
-      <c r="E59">
-        <v>48226</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B60" t="s">
-        <v>42</v>
-      </c>
-      <c r="C60" t="s">
-        <v>43</v>
-      </c>
-      <c r="D60" t="s">
-        <v>44</v>
-      </c>
-      <c r="E60">
-        <v>90026</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B61" t="s">
-        <v>81</v>
-      </c>
-      <c r="C61" t="s">
-        <v>64</v>
-      </c>
-      <c r="D61" t="s">
-        <v>65</v>
-      </c>
-      <c r="E61">
-        <v>10012</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B62" t="s">
-        <v>84</v>
-      </c>
-      <c r="C62" t="s">
         <v>85</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E58" t="s">
         <v>86</v>
       </c>
-      <c r="E62">
+      <c r="F58">
         <v>33132</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="4" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B67" s="3"/>
+      <c r="B63" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="B64" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C64" t="s">
+        <v>105</v>
+      </c>
+      <c r="D64" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B65" t="s">
+        <v>108</v>
+      </c>
+      <c r="C65" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
+        <v>109</v>
+      </c>
+      <c r="C66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
+        <v>110</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>125</v>
+      </c>
+      <c r="C68" t="s">
+        <v>20</v>
+      </c>
+      <c r="D68" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>111</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>132</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>104</v>
+      </c>
+      <c r="C82" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B84">
+        <v>2</v>
+      </c>
+      <c r="C84" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B85">
+        <v>3</v>
+      </c>
+      <c r="C85" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B86">
+        <v>6</v>
+      </c>
+      <c r="C86" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B87">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B88">
+        <v>5</v>
+      </c>
+      <c r="C88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="B95" s="10" t="s">
+        <v>133</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J19:J29">
@@ -2691,6 +2820,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
@@ -2699,15 +2837,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2952,20 +3081,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE6EC55-B0E7-4ACE-A5DA-E03DCA4973DE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
     <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
